--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrInvestAllInfo.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrInvestAllInfo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yitihua_idea\pingan-parent\pingan-entrust\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\tams-3.0\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>组合代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,6 +83,10 @@
   </si>
   <si>
     <t>清算速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>证券账户</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -437,26 +441,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.125" customWidth="1"/>
     <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="3" max="4" width="12.75" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10.75" customWidth="1"/>
-    <col min="7" max="7" width="11.375" customWidth="1"/>
-    <col min="8" max="8" width="13.125" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="34.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="14.25" customWidth="1"/>
-    <col min="13" max="14" width="12.875" customWidth="1"/>
-    <col min="15" max="15" width="10.625" customWidth="1"/>
-    <col min="16" max="16" width="23.75" customWidth="1"/>
+    <col min="3" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="10.75" customWidth="1"/>
+    <col min="8" max="8" width="11.375" customWidth="1"/>
+    <col min="9" max="9" width="13.125" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="34.5" style="3" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="14.25" customWidth="1"/>
+    <col min="14" max="15" width="12.875" customWidth="1"/>
+    <col min="16" max="16" width="10.625" customWidth="1"/>
+    <col min="17" max="17" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -467,44 +471,47 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="J2" s="5"/>
+    <row r="2" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="K2" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
